--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_230_R23.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_230_R23.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7208</v>
+        <v>3.9209</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8979</v>
+        <v>2.1653</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8228</v>
+        <v>1.7556</v>
       </c>
       <c r="G2" t="n">
         <v>-2.3121</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3523</v>
+        <v>0.5524</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2513</v>
+        <v>0.016</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6036</v>
+        <v>0.5364</v>
       </c>
       <c r="V2" t="n">
         <v>4.2888</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7624</v>
+        <v>1.9053</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4578</v>
+        <v>1.2625</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6953</v>
+        <v>0.6428</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5777</v>
+        <v>0.4245</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1056</v>
+        <v>1.6393</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4721</v>
+        <v>-1.2148</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5844</v>
+        <v>2.3898</v>
       </c>
       <c r="K3" t="n">
-        <v>0.474</v>
+        <v>1.6006</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1104</v>
+        <v>0.7892</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1621</v>
+        <v>-1.9654</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5796</v>
+        <v>0.0387</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5825</v>
+        <v>-2.004</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3917</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4639</v>
+        <v>-2.7834</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5541</v>
+        <v>-0.2693</v>
       </c>
       <c r="T3" t="n">
-        <v>2.265</v>
+        <v>-0.094</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2891</v>
+        <v>-0.1753</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3943</v>
+        <v>1.7501</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>1.7501</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.536</v>
+        <v>1.3859</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0948</v>
+        <v>2.1484</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4411</v>
+        <v>-0.7625</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4245</v>
+        <v>-1.5777</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6393</v>
+        <v>-0.1056</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2148</v>
+        <v>-1.4721</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3898</v>
+        <v>0.5844</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6006</v>
+        <v>0.474</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7892</v>
+        <v>0.1104</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9654</v>
+        <v>-2.1621</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0387</v>
+        <v>-0.5796</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.004</v>
+        <v>-1.5825</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7834</v>
+        <v>-0.4639</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6386</v>
+        <v>1.1775</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2617</v>
+        <v>0.9557</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3769</v>
+        <v>0.2219</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7501</v>
+        <v>0.3943</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7501</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1483</v>
+        <v>-0.2241</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9935</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8453</v>
+        <v>-1.0129</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0404</v>
+        <v>-1.9235</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0673</v>
+        <v>-0.09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0269</v>
+        <v>-1.8335</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8227</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4852</v>
+        <v>0.175</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6625</v>
+        <v>1.325</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2177</v>
+        <v>-3.4235</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4179</v>
+        <v>-0.2651</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-3.1584</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7834</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6781</v>
+        <v>-0.6201</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4708</v>
+        <v>-0.4793</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2074</v>
+        <v>-0.1408</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0401</v>
+        <v>-0.776</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0064</v>
+        <v>-1.2171</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0465</v>
+        <v>0.4411</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9235</v>
+        <v>-0.1929</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.09</v>
+        <v>0.2822</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8335</v>
+        <v>-0.4751</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>-0.1141</v>
       </c>
       <c r="K6" t="n">
-        <v>0.175</v>
+        <v>0.6722</v>
       </c>
       <c r="L6" t="n">
-        <v>1.325</v>
+        <v>-0.7863</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.4235</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2651</v>
+        <v>-0.39</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.1584</v>
+        <v>0.3113</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3195</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4361</v>
+        <v>0.118</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2617</v>
+        <v>0.1496</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1744</v>
+        <v>-0.0316</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.8608</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5002</v>
+        <v>-1.2652</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8069</v>
+        <v>0.8813</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3067</v>
+        <v>-2.1465</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1929</v>
+        <v>-2.6963</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2822</v>
+        <v>0.4189</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4751</v>
+        <v>-3.1151</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1141</v>
+        <v>-0.606</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6722</v>
+        <v>0.6624</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7863</v>
+        <v>-1.2683</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-2.0903</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.39</v>
+        <v>-0.2435</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3113</v>
+        <v>-1.8468</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.4639</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6062</v>
+        <v>0.2919</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4402</v>
+        <v>0.0593</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1661</v>
+        <v>0.2326</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8608</v>
+        <v>-0.2525</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7886</v>
+        <v>1.8919</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7587</v>
+        <v>-1.3546</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4214</v>
+        <v>-3.3343</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1801</v>
+        <v>1.9797</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6963</v>
+        <v>-1.0404</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4189</v>
+        <v>-1.0673</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.1151</v>
+        <v>0.0269</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.606</v>
+        <v>-0.8227</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6624</v>
+        <v>-1.4852</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2683</v>
+        <v>0.6625</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0903</v>
+        <v>-0.2177</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2435</v>
+        <v>0.4179</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8468</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4639</v>
+        <v>-2.7834</v>
       </c>
       <c r="R8" t="n">
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2016</v>
+        <v>0.4718</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4007</v>
+        <v>0.13</v>
       </c>
       <c r="U8" t="n">
-        <v>0.199</v>
+        <v>0.3418</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2525</v>
+        <v>0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8919</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.161</v>
+        <v>-1.9416</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0698</v>
+        <v>-0.716</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0912</v>
+        <v>-1.2256</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6201</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7187</v>
+        <v>-0.4993</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7468</v>
+        <v>-0.393</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0281</v>
+        <v>-0.1063</v>
       </c>
       <c r="V9" t="n">
         <v>-1.214</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9515</v>
+        <v>-6.071</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1436</v>
+        <v>-3.9942</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8079</v>
+        <v>-2.0768</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8336</v>
@@ -1234,13 +1234,13 @@
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8821</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3541</v>
+        <v>0.5034</v>
       </c>
       <c r="U10" t="n">
-        <v>0.528</v>
+        <v>0.2592</v>
       </c>
       <c r="V10" t="n">
         <v>-2.6805</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5406</v>
+        <v>-4.4204</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1355</v>
+        <v>-2.015300000000001</v>
       </c>
       <c r="F11" t="n">
         <v>-2.4051</v>
@@ -1285,10 +1285,10 @@
         <v>-16.2947</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3782000000000001</v>
+        <v>0.3782000000000003</v>
       </c>
       <c r="K11" t="n">
-        <v>5.063700000000001</v>
+        <v>5.0637</v>
       </c>
       <c r="L11" t="n">
         <v>-4.6854</v>
@@ -1303,7 +1303,7 @@
         <v>-11.6091</v>
       </c>
       <c r="P11" t="n">
-        <v>5.798800000000002</v>
+        <v>5.7988</v>
       </c>
       <c r="Q11" t="n">
         <v>-11.5976</v>
@@ -1312,13 +1312,13 @@
         <v>17.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8653999999999998</v>
+        <v>1.9855</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2724999999999998</v>
+        <v>0.8476999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1378</v>
+        <v>1.1379</v>
       </c>
       <c r="V11" t="n">
         <v>0.5672000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.3279</v>
+        <v>7.619</v>
       </c>
       <c r="E12" t="n">
-        <v>6.7033</v>
+        <v>7.411</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3754</v>
+        <v>0.208</v>
       </c>
       <c r="G12" t="n">
         <v>8.030099999999999</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6843</v>
+        <v>-0.3932</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9709</v>
+        <v>-0.2631</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7134</v>
+        <v>-0.13</v>
       </c>
       <c r="V12" t="n">
         <v>0.6778999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9554</v>
+        <v>3.7201</v>
       </c>
       <c r="E13" t="n">
         <v>2.0507</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9047</v>
+        <v>1.6694</v>
       </c>
       <c r="G13" t="n">
         <v>0.979</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5821</v>
+        <v>0.3468</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4086</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9906</v>
+        <v>0.7554</v>
       </c>
       <c r="V13" t="n">
         <v>1.4665</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7657</v>
+        <v>3.1245</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1573</v>
+        <v>2.8838</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.2407</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9747</v>
+        <v>3.405</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8894</v>
+        <v>-0.8377</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8641</v>
+        <v>4.2427</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9709</v>
+        <v>3.1588</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6351</v>
+        <v>0.0672</v>
       </c>
       <c r="L14" t="n">
-        <v>1.606</v>
+        <v>3.0916</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0039</v>
+        <v>0.2462</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2543</v>
+        <v>-0.9049</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2582</v>
+        <v>1.1511</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0672</v>
+        <v>-0.2959</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1142</v>
+        <v>-0.275</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1814</v>
+        <v>-0.0209</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3943</v>
+        <v>-1.6083</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2374</v>
+        <v>3.0403</v>
       </c>
       <c r="E15" t="n">
-        <v>2.412</v>
+        <v>2.0393</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1747</v>
+        <v>1.001</v>
       </c>
       <c r="G15" t="n">
-        <v>3.405</v>
+        <v>1.9747</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8377</v>
+        <v>-0.8894</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2427</v>
+        <v>2.8641</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1588</v>
+        <v>0.9709</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0672</v>
+        <v>-0.6351</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0916</v>
+        <v>1.606</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2462</v>
+        <v>1.0039</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9049</v>
+        <v>-0.2543</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1511</v>
+        <v>1.2582</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.183</v>
+        <v>0.2074</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7468</v>
+        <v>-0.0037</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4362</v>
+        <v>0.2111</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.6083</v>
+        <v>0.3943</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6083</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2405</v>
+        <v>1.0934</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7861</v>
+        <v>-0.5502</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0266</v>
+        <v>1.6436</v>
       </c>
       <c r="G16" t="n">
         <v>3.2966</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2727</v>
+        <v>-0.4197</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5258</v>
+        <v>0.0912</v>
       </c>
       <c r="V16" t="n">
         <v>0.5361</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1932</v>
+        <v>-0.2057</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-1.1397</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7431</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>0.7969000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.4766</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5272</v>
+        <v>-0.0626</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3484</v>
+        <v>0.5392</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-1.8703</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3164</v>
+        <v>-0.9811</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8784</v>
+        <v>-0.8892</v>
       </c>
       <c r="G18" t="n">
         <v>0.2201</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8262</v>
+        <v>0.5179</v>
       </c>
       <c r="T18" t="n">
-        <v>2.135</v>
+        <v>0.8375</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3088</v>
+        <v>-0.3196</v>
       </c>
       <c r="V18" t="n">
         <v>-2.1444</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4696</v>
+        <v>-2.0422</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8025</v>
+        <v>-2.3307</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3329</v>
+        <v>0.2885</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4738</v>
@@ -1936,13 +1936,13 @@
         <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.622</v>
+        <v>-0.1946</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8962</v>
+        <v>-0.4244</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2741</v>
+        <v>0.2298</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6778999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2028</v>
+        <v>-3.5059</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5015</v>
+        <v>-2.7374</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7013</v>
+        <v>-0.7685</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7044</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5017</v>
+        <v>0.1986</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4876</v>
+        <v>0.2517</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0141</v>
+        <v>-0.0532</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.945</v>
+        <v>-3.86</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1307</v>
+        <v>-4.7769</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1857</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7523</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1784</v>
+        <v>0.2634</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.2787</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.5421</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2836</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>5.540700000000001</v>
+        <v>7.113200000000003</v>
       </c>
       <c r="E22" t="n">
-        <v>1.868999999999999</v>
+        <v>1.868799999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>3.6716</v>
+        <v>5.244299999999999</v>
       </c>
       <c r="G22" t="n">
         <v>12.7719</v>
@@ -2170,13 +2170,13 @@
         <v>11.5979</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8652999999999996</v>
+        <v>0.7073</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1379</v>
+        <v>-1.1378</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2726000000000001</v>
+        <v>1.8451</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5672000000000001</v>
